--- a/erp-server/erp-server-wms/src/main/resources/excel/pdaMoveInfo.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/pdaMoveInfo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="21240" windowHeight="11265"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -741,7 +741,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -749,10 +749,19 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1288,8 +1297,8 @@
     <col min="5" max="5" width="22.375" customWidth="1"/>
     <col min="6" max="6" width="16.875" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="25.5" customWidth="1"/>
-    <col min="9" max="9" width="26.25" customWidth="1"/>
+    <col min="8" max="8" width="25.5" style="3" customWidth="1"/>
+    <col min="9" max="9" width="26.25" style="3" customWidth="1"/>
     <col min="10" max="10" width="16.875" customWidth="1"/>
     <col min="11" max="11" width="21.375" customWidth="1"/>
     <col min="12" max="12" width="20.875" customWidth="1"/>
@@ -1298,46 +1307,46 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:14">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1363,10 +1372,10 @@
       <c r="G2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="6" t="s">
         <v>22</v>
       </c>
       <c r="J2" s="2" t="s">

--- a/erp-server/erp-server-wms/src/main/resources/excel/pdaMoveInfo.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/pdaMoveInfo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21240" windowHeight="11265"/>
+    <workbookView windowWidth="22890" windowHeight="11265"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>单据单号</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>{.approveUserName}</t>
+  </si>
+  <si>
+    <t>{.createUserName}</t>
   </si>
   <si>
     <t>{.createTime}</t>
@@ -1385,13 +1388,13 @@
         <v>24</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/pdaMoveInfo.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/pdaMoveInfo.xlsx
@@ -59,7 +59,10 @@
     <t>备注</t>
   </si>
   <si>
-    <t>审核人</t>
+    <t>审核人(最新)</t>
+  </si>
+  <si>
+    <t>审核完成时间</t>
   </si>
   <si>
     <t>创建人</t>
@@ -68,9 +71,6 @@
     <t>创建时间</t>
   </si>
   <si>
-    <t>审核完成时间</t>
-  </si>
-  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -104,13 +104,13 @@
     <t>{.approveUserName}</t>
   </si>
   <si>
+    <t>{.approveTime}</t>
+  </si>
+  <si>
     <t>{.createUserName}</t>
   </si>
   <si>
     <t>{.createTime}</t>
-  </si>
-  <si>
-    <t>{.approveTime}</t>
   </si>
 </sst>
 </file>
@@ -1304,9 +1304,9 @@
     <col min="9" max="9" width="26.25" style="3" customWidth="1"/>
     <col min="10" max="10" width="16.875" customWidth="1"/>
     <col min="11" max="11" width="21.375" customWidth="1"/>
-    <col min="12" max="12" width="20.875" customWidth="1"/>
-    <col min="13" max="13" width="17.25" customWidth="1"/>
-    <col min="14" max="14" width="17" customWidth="1"/>
+    <col min="12" max="12" width="17" customWidth="1"/>
+    <col min="13" max="13" width="20.875" customWidth="1"/>
+    <col min="14" max="14" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:14">
